--- a/AAII_Financials/Yearly/ABBNY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ABBNY_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -653,135 +653,147 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:L102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L7" s="2"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>32235000</v>
+      </c>
+      <c r="E8" s="3">
         <v>29446000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>28945000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>26134000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>27978000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>27662000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>25196000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>24929000</v>
       </c>
-      <c r="K8" s="3"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L8" s="3"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>20956000</v>
+      </c>
+      <c r="E9" s="3">
         <v>19712000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>19407000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>18123000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>19018000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>19059000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>17184000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>17384000</v>
       </c>
-      <c r="K9" s="3"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L9" s="3"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>11279000</v>
+      </c>
+      <c r="E10" s="3">
         <v>9734000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>9538000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>8011000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>8960000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>8603000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>8012000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>7545000</v>
       </c>
-      <c r="K10" s="3"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L10" s="3"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -793,35 +805,39 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>1307000</v>
+      </c>
+      <c r="E12" s="3">
         <v>1164000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1215000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1111000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1198000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>1141000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1013000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>956000</v>
       </c>
-      <c r="K12" s="3"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L12" s="3"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -846,36 +862,42 @@
       <c r="J13" s="3">
         <v>0</v>
       </c>
-      <c r="K13" s="3"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K13" s="3">
+        <v>0</v>
+      </c>
+      <c r="L13" s="3"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>124000</v>
+      </c>
+      <c r="E14" s="3">
         <v>301000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-2043000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>817000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>71000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>106000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>8000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>196000</v>
       </c>
-      <c r="K14" s="3"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L14" s="3"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -900,9 +922,12 @@
       <c r="J15" s="3">
         <v>0</v>
       </c>
-      <c r="K15" s="3"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K15" s="3">
+        <v>0</v>
+      </c>
+      <c r="L15" s="3"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -911,62 +936,69 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+    </row>
+    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>27364000</v>
+      </c>
+      <c r="E17" s="3">
         <v>26109000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>23227000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>24703000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>26040000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>25436000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>22966000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>23000000</v>
       </c>
-      <c r="K17" s="3"/>
-    </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L17" s="3"/>
+    </row>
+    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>4871000</v>
+      </c>
+      <c r="E18" s="3">
         <v>3337000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>5718000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1431000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1938000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>2226000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>2230000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1929000</v>
       </c>
-      <c r="K18" s="3"/>
-    </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L18" s="3"/>
+    </row>
+    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -978,143 +1010,159 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+    </row>
+    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-63000</v>
+      </c>
+      <c r="E20" s="3">
         <v>94000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>106000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-142000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>17000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>198000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>126000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-9000</v>
       </c>
-      <c r="K20" s="3"/>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L20" s="3"/>
+    </row>
+    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>5588000</v>
+      </c>
+      <c r="E21" s="3">
         <v>4245000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>6717000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>2204000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>2916000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>3340000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>3192000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2790000</v>
       </c>
-      <c r="K21" s="3"/>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L21" s="3"/>
+    </row>
+    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
-        <v>37000</v>
+        <v>30000</v>
       </c>
       <c r="E22" s="3">
         <v>37000</v>
       </c>
       <c r="F22" s="3">
+        <v>37000</v>
+      </c>
+      <c r="G22" s="3">
         <v>448000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>93000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>305000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>254000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>159000</v>
       </c>
-      <c r="K22" s="3"/>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L22" s="3"/>
+    </row>
+    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>4778000</v>
+      </c>
+      <c r="E23" s="3">
         <v>3394000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>5787000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>841000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1862000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>2119000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2102000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1761000</v>
       </c>
-      <c r="K23" s="3"/>
-    </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L23" s="3"/>
+    </row>
+    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>930000</v>
+      </c>
+      <c r="E24" s="3">
         <v>757000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1057000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>496000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>772000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>544000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>587000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>526000</v>
       </c>
-      <c r="K24" s="3"/>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L24" s="3"/>
+    </row>
+    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1139,63 +1187,72 @@
       <c r="J25" s="3">
         <v>0</v>
       </c>
-      <c r="K25" s="3"/>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K25" s="3">
+        <v>0</v>
+      </c>
+      <c r="L25" s="3"/>
+    </row>
+    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>3848000</v>
+      </c>
+      <c r="E26" s="3">
         <v>2637000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>4730000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>345000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1090000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1575000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1515000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1235000</v>
       </c>
-      <c r="K26" s="3"/>
-    </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L26" s="3"/>
+    </row>
+    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>3769000</v>
+      </c>
+      <c r="E27" s="3">
         <v>2518000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>4626000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>294000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1043000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1450000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1363000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1100000</v>
       </c>
-      <c r="K27" s="3"/>
-    </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L27" s="3"/>
+    </row>
+    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1220,36 +1277,42 @@
       <c r="J28" s="3">
         <v>0</v>
       </c>
-      <c r="K28" s="3"/>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K28" s="3">
+        <v>0</v>
+      </c>
+      <c r="L28" s="3"/>
+    </row>
+    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D29" s="3">
+        <v>-24000</v>
+      </c>
+      <c r="E29" s="3">
         <v>-43000</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>-80000</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>4852000</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>396000</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>723000</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>844000</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>815000</v>
       </c>
-      <c r="K29" s="3"/>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L29" s="3"/>
+    </row>
+    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -1274,9 +1337,12 @@
       <c r="J30" s="3">
         <v>0</v>
       </c>
-      <c r="K30" s="3"/>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K30" s="3">
+        <v>0</v>
+      </c>
+      <c r="L30" s="3"/>
+    </row>
+    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -1301,63 +1367,72 @@
       <c r="J31" s="3">
         <v>0</v>
       </c>
-      <c r="K31" s="3"/>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K31" s="3">
+        <v>0</v>
+      </c>
+      <c r="L31" s="3"/>
+    </row>
+    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>63000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-94000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-106000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>142000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-17000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-198000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-126000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>9000</v>
       </c>
-      <c r="K32" s="3"/>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L32" s="3"/>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>3745000</v>
+      </c>
+      <c r="E33" s="3">
         <v>2475000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>4546000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>5146000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1439000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>2173000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>2207000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1915000</v>
       </c>
-      <c r="K33" s="3"/>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L33" s="3"/>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -1382,68 +1457,77 @@
       <c r="J34" s="3">
         <v>0</v>
       </c>
-      <c r="K34" s="3"/>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K34" s="3">
+        <v>0</v>
+      </c>
+      <c r="L34" s="3"/>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>3745000</v>
+      </c>
+      <c r="E35" s="3">
         <v>2475000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>4546000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>5146000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1439000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>2173000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>2207000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1915000</v>
       </c>
-      <c r="K35" s="3"/>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L35" s="3"/>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2"/>
-    </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L38" s="2"/>
+    </row>
+    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -1455,8 +1539,9 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -1468,251 +1553,279 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>3891000</v>
+      </c>
+      <c r="E41" s="3">
         <v>4156000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>4159000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3278000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3544000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3445000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>4526000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3644000</v>
       </c>
-      <c r="K41" s="3"/>
-    </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L41" s="3"/>
+    </row>
+    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
+        <v>2087000</v>
+      </c>
+      <c r="E42" s="3">
         <v>894000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>1308000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>2400000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>675000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>852000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1263000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>2209000</v>
       </c>
-      <c r="K42" s="3"/>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L42" s="3"/>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>8536000</v>
+      </c>
+      <c r="E43" s="3">
         <v>7812000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>7541000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>7805000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>7459000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>7468000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>17418000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>9696000</v>
       </c>
-      <c r="K43" s="3"/>
-    </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L43" s="3"/>
+    </row>
+    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>6149000</v>
+      </c>
+      <c r="E44" s="3">
         <v>6028000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>4880000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>4469000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>4184000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>4284000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>8796000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>4347000</v>
       </c>
-      <c r="K44" s="3"/>
-    </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L44" s="3"/>
+    </row>
+    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
+        <v>614000</v>
+      </c>
+      <c r="E45" s="3">
         <v>680000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>807000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1274000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>10596000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>5816000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>5607000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2044000</v>
       </c>
-      <c r="K45" s="3"/>
-    </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L45" s="3"/>
+    </row>
+    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>21277000</v>
+      </c>
+      <c r="E46" s="3">
         <v>19570000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>18695000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>19226000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>26458000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>21865000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>22135000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>21052000</v>
       </c>
-      <c r="K46" s="3"/>
-    </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L46" s="3"/>
+    </row>
+    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
+        <v>222000</v>
+      </c>
+      <c r="E47" s="3">
         <v>157000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1691000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1808000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>81000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>142000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>559000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>394000</v>
       </c>
-      <c r="K47" s="3"/>
-    </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L47" s="3"/>
+    </row>
+    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>5035000</v>
+      </c>
+      <c r="E48" s="3">
         <v>4752000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4940000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>5143000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4966000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4133000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>9167000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4743000</v>
       </c>
-      <c r="K48" s="3"/>
-    </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L48" s="3"/>
+    </row>
+    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>11784000</v>
+      </c>
+      <c r="E49" s="3">
         <v>11917000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>12043000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>12928000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>13077000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>13371000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>14583000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>11497000</v>
       </c>
-      <c r="K49" s="3"/>
-    </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L49" s="3"/>
+    </row>
+    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -1737,9 +1850,12 @@
       <c r="J50" s="3">
         <v>0</v>
       </c>
-      <c r="K50" s="3"/>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K50" s="3">
+        <v>0</v>
+      </c>
+      <c r="L50" s="3"/>
+    </row>
+    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -1764,36 +1880,42 @@
       <c r="J51" s="3">
         <v>0</v>
       </c>
-      <c r="K51" s="3"/>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K51" s="3">
+        <v>0</v>
+      </c>
+      <c r="L51" s="3"/>
+    </row>
+    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
+        <v>2622000</v>
+      </c>
+      <c r="E52" s="3">
         <v>2752000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2891000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1983000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1526000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>4930000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>5171000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1516000</v>
       </c>
-      <c r="K52" s="3"/>
-    </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L52" s="3"/>
+    </row>
+    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -1818,36 +1940,42 @@
       <c r="J53" s="3">
         <v>0</v>
       </c>
-      <c r="K53" s="3"/>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K53" s="3">
+        <v>0</v>
+      </c>
+      <c r="L53" s="3"/>
+    </row>
+    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>40940000</v>
+      </c>
+      <c r="E54" s="3">
         <v>39148000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>40260000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>41088000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>46108000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>44441000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>43458000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>39202000</v>
       </c>
-      <c r="K54" s="3"/>
-    </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L54" s="3"/>
+    </row>
+    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -1859,8 +1987,9 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+    </row>
+    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -1872,170 +2001,189 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+    </row>
+    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>4847000</v>
+      </c>
+      <c r="E57" s="3">
         <v>4904000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4921000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4571000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4353000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4424000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3736000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>4446000</v>
       </c>
-      <c r="K57" s="3"/>
-    </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L57" s="3"/>
+    </row>
+    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
+        <v>2607000</v>
+      </c>
+      <c r="E58" s="3">
         <v>2535000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1384000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1293000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2287000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2031000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>726000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1003000</v>
       </c>
-      <c r="K58" s="3"/>
-    </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L58" s="3"/>
+    </row>
+    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
+        <v>10550000</v>
+      </c>
+      <c r="E59" s="3">
         <v>9090000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>9263000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>9552000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>13626000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>11992000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>14625000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>10501000</v>
       </c>
-      <c r="K59" s="3"/>
-    </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L59" s="3"/>
+    </row>
+    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>18004000</v>
+      </c>
+      <c r="E60" s="3">
         <v>16529000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>15568000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>15416000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>20266000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>18447000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>16469000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>15149000</v>
       </c>
-      <c r="K60" s="3"/>
-    </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L60" s="3"/>
+    </row>
+    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
+        <v>5221000</v>
+      </c>
+      <c r="E61" s="3">
         <v>5143000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4177000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4828000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>6772000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>6587000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>6682000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>5800000</v>
       </c>
-      <c r="K61" s="3"/>
-    </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L61" s="3"/>
+    </row>
+    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
+        <v>3569000</v>
+      </c>
+      <c r="E62" s="3">
         <v>4184000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>4515000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>4648000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>5090000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>4444000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>6370000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>7524000</v>
       </c>
-      <c r="K62" s="3"/>
-    </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L62" s="3"/>
+    </row>
+    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -2060,9 +2208,12 @@
       <c r="J63" s="3">
         <v>0</v>
       </c>
-      <c r="K63" s="3"/>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K63" s="3">
+        <v>0</v>
+      </c>
+      <c r="L63" s="3"/>
+    </row>
+    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -2087,9 +2238,12 @@
       <c r="J64" s="3">
         <v>0</v>
       </c>
-      <c r="K64" s="3"/>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K64" s="3">
+        <v>0</v>
+      </c>
+      <c r="L64" s="3"/>
+    </row>
+    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -2114,36 +2268,42 @@
       <c r="J65" s="3">
         <v>0</v>
       </c>
-      <c r="K65" s="3"/>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K65" s="3">
+        <v>0</v>
+      </c>
+      <c r="L65" s="3"/>
+    </row>
+    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>27530000</v>
+      </c>
+      <c r="E66" s="3">
         <v>26371000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>24681000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>25403000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>32582000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>30489000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>28639000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>25807000</v>
       </c>
-      <c r="K66" s="3"/>
-    </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L66" s="3"/>
+    </row>
+    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -2155,8 +2315,9 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+    </row>
+    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -2181,9 +2342,12 @@
       <c r="J68" s="3">
         <v>0</v>
       </c>
-      <c r="K68" s="3"/>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K68" s="3">
+        <v>0</v>
+      </c>
+      <c r="L68" s="3"/>
+    </row>
+    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -2208,9 +2372,12 @@
       <c r="J69" s="3">
         <v>0</v>
       </c>
-      <c r="K69" s="3"/>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K69" s="3">
+        <v>0</v>
+      </c>
+      <c r="L69" s="3"/>
+    </row>
+    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -2235,9 +2402,12 @@
       <c r="J70" s="3">
         <v>0</v>
       </c>
-      <c r="K70" s="3"/>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K70" s="3">
+        <v>0</v>
+      </c>
+      <c r="L70" s="3"/>
+    </row>
+    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -2262,36 +2432,42 @@
       <c r="J71" s="3">
         <v>0</v>
       </c>
-      <c r="K71" s="3"/>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K71" s="3">
+        <v>0</v>
+      </c>
+      <c r="L71" s="3"/>
+    </row>
+    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>19724000</v>
+      </c>
+      <c r="E72" s="3">
         <v>20082000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>22477000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>22946000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>19640000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>19839000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>19594000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>19925000</v>
       </c>
-      <c r="K72" s="3"/>
-    </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L72" s="3"/>
+    </row>
+    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -2316,9 +2492,12 @@
       <c r="J73" s="3">
         <v>0</v>
       </c>
-      <c r="K73" s="3"/>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K73" s="3">
+        <v>0</v>
+      </c>
+      <c r="L73" s="3"/>
+    </row>
+    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -2343,9 +2522,12 @@
       <c r="J74" s="3">
         <v>0</v>
       </c>
-      <c r="K74" s="3"/>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K74" s="3">
+        <v>0</v>
+      </c>
+      <c r="L74" s="3"/>
+    </row>
+    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -2370,36 +2552,42 @@
       <c r="J75" s="3">
         <v>0</v>
       </c>
-      <c r="K75" s="3"/>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K75" s="3">
+        <v>0</v>
+      </c>
+      <c r="L75" s="3"/>
+    </row>
+    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>13410000</v>
+      </c>
+      <c r="E76" s="3">
         <v>12777000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>15579000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>15685000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>13526000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>13952000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>14819000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>13395000</v>
       </c>
-      <c r="K76" s="3"/>
-    </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L76" s="3"/>
+    </row>
+    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -2424,68 +2612,77 @@
       <c r="J77" s="3">
         <v>0</v>
       </c>
-      <c r="K77" s="3"/>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K77" s="3">
+        <v>0</v>
+      </c>
+      <c r="L77" s="3"/>
+    </row>
+    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2"/>
-    </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L80" s="2"/>
+    </row>
+    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>3745000</v>
+      </c>
+      <c r="E81" s="3">
         <v>2475000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>4546000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>5146000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1439000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>2173000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>2207000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1915000</v>
       </c>
-      <c r="K81" s="3"/>
-    </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L81" s="3"/>
+    </row>
+    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -2497,35 +2694,39 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+    </row>
+    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
+        <v>780000</v>
+      </c>
+      <c r="E83" s="3">
         <v>814000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>893000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>915000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>961000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>916000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>836000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>870000</v>
       </c>
-      <c r="K83" s="3"/>
-    </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L83" s="3"/>
+    </row>
+    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -2550,9 +2751,12 @@
       <c r="J84" s="3">
         <v>0</v>
       </c>
-      <c r="K84" s="3"/>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K84" s="3">
+        <v>0</v>
+      </c>
+      <c r="L84" s="3"/>
+    </row>
+    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -2577,9 +2781,12 @@
       <c r="J85" s="3">
         <v>0</v>
       </c>
-      <c r="K85" s="3"/>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K85" s="3">
+        <v>0</v>
+      </c>
+      <c r="L85" s="3"/>
+    </row>
+    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -2604,9 +2811,12 @@
       <c r="J86" s="3">
         <v>0</v>
       </c>
-      <c r="K86" s="3"/>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K86" s="3">
+        <v>0</v>
+      </c>
+      <c r="L86" s="3"/>
+    </row>
+    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -2631,9 +2841,12 @@
       <c r="J87" s="3">
         <v>0</v>
       </c>
-      <c r="K87" s="3"/>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K87" s="3">
+        <v>0</v>
+      </c>
+      <c r="L87" s="3"/>
+    </row>
+    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -2658,36 +2871,42 @@
       <c r="J88" s="3">
         <v>0</v>
       </c>
-      <c r="K88" s="3"/>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K88" s="3">
+        <v>0</v>
+      </c>
+      <c r="L88" s="3"/>
+    </row>
+    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>4290000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1287000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>3330000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1693000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2325000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2924000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>3799000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>3843000</v>
       </c>
-      <c r="K89" s="3"/>
-    </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L89" s="3"/>
+    </row>
+    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -2699,35 +2918,39 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+    </row>
+    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-770000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-762000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-820000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-694000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-762000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-772000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-752000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-632000</v>
       </c>
-      <c r="K91" s="3"/>
-    </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L91" s="3"/>
+    </row>
+    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -2752,9 +2975,12 @@
       <c r="J92" s="3">
         <v>0</v>
       </c>
-      <c r="K92" s="3"/>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K92" s="3">
+        <v>0</v>
+      </c>
+      <c r="L92" s="3"/>
+    </row>
+    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -2779,36 +3005,42 @@
       <c r="J93" s="3">
         <v>0</v>
       </c>
-      <c r="K93" s="3"/>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K93" s="3">
+        <v>0</v>
+      </c>
+      <c r="L93" s="3"/>
+    </row>
+    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>-1615000</v>
+      </c>
+      <c r="E94" s="3">
         <v>981000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>2307000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>6760000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-815000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-3085000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1450000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1305000</v>
       </c>
-      <c r="K94" s="3"/>
-    </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L94" s="3"/>
+    </row>
+    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -2820,35 +3052,39 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+    </row>
+    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D96" s="3">
+        <v>-1713000</v>
+      </c>
+      <c r="E96" s="3">
         <v>-1698000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-1726000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-1736000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-1675000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-1717000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-1635000</v>
       </c>
-      <c r="J96" s="3">
-        <v>0</v>
-      </c>
-      <c r="K96" s="3"/>
-    </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3"/>
+    </row>
+    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -2873,9 +3109,12 @@
       <c r="J97" s="3">
         <v>0</v>
       </c>
-      <c r="K97" s="3"/>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K97" s="3">
+        <v>0</v>
+      </c>
+      <c r="L97" s="3"/>
+    </row>
+    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -2900,9 +3139,12 @@
       <c r="J98" s="3">
         <v>0</v>
       </c>
-      <c r="K98" s="3"/>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K98" s="3">
+        <v>0</v>
+      </c>
+      <c r="L98" s="3"/>
+    </row>
+    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -2927,88 +3169,100 @@
       <c r="J99" s="3">
         <v>0</v>
       </c>
-      <c r="K99" s="3"/>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K99" s="3">
+        <v>0</v>
+      </c>
+      <c r="L99" s="3"/>
+    </row>
+    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>-2897000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2394000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-4968000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-8175000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1383000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-789000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1735000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-3355000</v>
       </c>
-      <c r="K100" s="3"/>
-    </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L100" s="3"/>
+    </row>
+    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
+        <v>-43000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-189000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-81000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>79000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-28000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-131000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>268000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-104000</v>
       </c>
-      <c r="K101" s="3"/>
-    </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L101" s="3"/>
+    </row>
+    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>-265000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-315000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>588000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>357000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>99000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1081000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>882000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-921000</v>
       </c>
-      <c r="K102" s="3"/>
+      <c r="L102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/ABBNY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ABBNY_YR_FIN.xlsx
@@ -756,7 +756,7 @@
         <v>19059000</v>
       </c>
       <c r="J9" s="3">
-        <v>17184000</v>
+        <v>17278000</v>
       </c>
       <c r="K9" s="3">
         <v>17384000</v>
@@ -786,7 +786,7 @@
         <v>8603000</v>
       </c>
       <c r="J10" s="3">
-        <v>8012000</v>
+        <v>7918000</v>
       </c>
       <c r="K10" s="3">
         <v>7545000</v>
@@ -812,25 +812,25 @@
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>1307000</v>
+        <v>1314000</v>
       </c>
       <c r="E12" s="3">
         <v>1164000</v>
       </c>
       <c r="F12" s="3">
-        <v>1215000</v>
+        <v>1217000</v>
       </c>
       <c r="G12" s="3">
-        <v>1111000</v>
+        <v>1113000</v>
       </c>
       <c r="H12" s="3">
-        <v>1198000</v>
+        <v>1197000</v>
       </c>
       <c r="I12" s="3">
-        <v>1141000</v>
+        <v>1142000</v>
       </c>
       <c r="J12" s="3">
-        <v>1013000</v>
+        <v>1018000</v>
       </c>
       <c r="K12" s="3">
         <v>956000</v>
@@ -872,25 +872,25 @@
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>124000</v>
+        <v>-31000</v>
       </c>
       <c r="E14" s="3">
-        <v>301000</v>
+        <v>176000</v>
       </c>
       <c r="F14" s="3">
-        <v>-2043000</v>
+        <v>-2164000</v>
       </c>
       <c r="G14" s="3">
-        <v>817000</v>
+        <v>718000</v>
       </c>
       <c r="H14" s="3">
-        <v>71000</v>
+        <v>458000</v>
       </c>
       <c r="I14" s="3">
-        <v>106000</v>
+        <v>67000</v>
       </c>
       <c r="J14" s="3">
-        <v>8000</v>
+        <v>-185000</v>
       </c>
       <c r="K14" s="3">
         <v>196000</v>
@@ -902,25 +902,25 @@
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>736000</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>762000</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>827000</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>854000</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>887000</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>857000</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>786000</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -943,25 +943,25 @@
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>27364000</v>
+        <v>27371000</v>
       </c>
       <c r="E17" s="3">
-        <v>26109000</v>
+        <v>25757000</v>
       </c>
       <c r="F17" s="3">
-        <v>23227000</v>
+        <v>25116000</v>
       </c>
       <c r="G17" s="3">
-        <v>24703000</v>
+        <v>24320000</v>
       </c>
       <c r="H17" s="3">
-        <v>26040000</v>
+        <v>25518000</v>
       </c>
       <c r="I17" s="3">
-        <v>25436000</v>
+        <v>25292000</v>
       </c>
       <c r="J17" s="3">
-        <v>22966000</v>
+        <v>23053000</v>
       </c>
       <c r="K17" s="3">
         <v>23000000</v>
@@ -973,25 +973,25 @@
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>4871000</v>
+        <v>4864000</v>
       </c>
       <c r="E18" s="3">
-        <v>3337000</v>
+        <v>3689000</v>
       </c>
       <c r="F18" s="3">
-        <v>5718000</v>
+        <v>3829000</v>
       </c>
       <c r="G18" s="3">
-        <v>1431000</v>
+        <v>1814000</v>
       </c>
       <c r="H18" s="3">
-        <v>1938000</v>
+        <v>2460000</v>
       </c>
       <c r="I18" s="3">
-        <v>2226000</v>
+        <v>2370000</v>
       </c>
       <c r="J18" s="3">
-        <v>2230000</v>
+        <v>2143000</v>
       </c>
       <c r="K18" s="3">
         <v>1929000</v>
@@ -1017,25 +1017,25 @@
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>-63000</v>
+        <v>271000</v>
       </c>
       <c r="E20" s="3">
-        <v>94000</v>
+        <v>194000</v>
       </c>
       <c r="F20" s="3">
-        <v>106000</v>
+        <v>255000</v>
       </c>
       <c r="G20" s="3">
         <v>-142000</v>
       </c>
       <c r="H20" s="3">
-        <v>17000</v>
+        <v>114000</v>
       </c>
       <c r="I20" s="3">
-        <v>198000</v>
+        <v>-49000</v>
       </c>
       <c r="J20" s="3">
-        <v>126000</v>
+        <v>45000</v>
       </c>
       <c r="K20" s="3">
         <v>-9000</v>
@@ -1047,25 +1047,25 @@
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>5588000</v>
+        <v>5329000</v>
       </c>
       <c r="E21" s="3">
-        <v>4245000</v>
+        <v>4257000</v>
       </c>
       <c r="F21" s="3">
-        <v>6717000</v>
+        <v>4401000</v>
       </c>
       <c r="G21" s="3">
-        <v>2204000</v>
+        <v>2810000</v>
       </c>
       <c r="H21" s="3">
-        <v>2916000</v>
+        <v>3233000</v>
       </c>
       <c r="I21" s="3">
-        <v>3340000</v>
+        <v>3276000</v>
       </c>
       <c r="J21" s="3">
-        <v>3192000</v>
+        <v>2884000</v>
       </c>
       <c r="K21" s="3">
         <v>2790000</v>
@@ -1077,13 +1077,13 @@
         <v>16</v>
       </c>
       <c r="D22" s="3">
-        <v>30000</v>
+        <v>11000</v>
       </c>
       <c r="E22" s="3">
-        <v>37000</v>
+        <v>3000</v>
       </c>
       <c r="F22" s="3">
-        <v>37000</v>
+        <v>2000</v>
       </c>
       <c r="G22" s="3">
         <v>448000</v>
@@ -1155,7 +1155,7 @@
         <v>544000</v>
       </c>
       <c r="J24" s="3">
-        <v>587000</v>
+        <v>583000</v>
       </c>
       <c r="K24" s="3">
         <v>526000</v>
@@ -1215,7 +1215,7 @@
         <v>1575000</v>
       </c>
       <c r="J26" s="3">
-        <v>1515000</v>
+        <v>1519000</v>
       </c>
       <c r="K26" s="3">
         <v>1235000</v>
@@ -1227,25 +1227,25 @@
         <v>21</v>
       </c>
       <c r="D27" s="3">
-        <v>3769000</v>
+        <v>3745000</v>
       </c>
       <c r="E27" s="3">
-        <v>2518000</v>
+        <v>2475000</v>
       </c>
       <c r="F27" s="3">
-        <v>4626000</v>
+        <v>4546000</v>
       </c>
       <c r="G27" s="3">
-        <v>294000</v>
+        <v>5146000</v>
       </c>
       <c r="H27" s="3">
-        <v>1043000</v>
+        <v>1439000</v>
       </c>
       <c r="I27" s="3">
-        <v>1450000</v>
+        <v>2173000</v>
       </c>
       <c r="J27" s="3">
-        <v>1363000</v>
+        <v>2213000</v>
       </c>
       <c r="K27" s="3">
         <v>1100000</v>
@@ -1296,16 +1296,16 @@
         <v>-80000</v>
       </c>
       <c r="G29" s="3">
-        <v>4852000</v>
+        <v>4860000</v>
       </c>
       <c r="H29" s="3">
-        <v>396000</v>
+        <v>438000</v>
       </c>
       <c r="I29" s="3">
         <v>723000</v>
       </c>
       <c r="J29" s="3">
-        <v>844000</v>
+        <v>846000</v>
       </c>
       <c r="K29" s="3">
         <v>815000</v>
@@ -1377,25 +1377,25 @@
         <v>26</v>
       </c>
       <c r="D32" s="3">
-        <v>63000</v>
+        <v>-271000</v>
       </c>
       <c r="E32" s="3">
-        <v>-94000</v>
+        <v>-194000</v>
       </c>
       <c r="F32" s="3">
-        <v>-106000</v>
+        <v>-255000</v>
       </c>
       <c r="G32" s="3">
         <v>142000</v>
       </c>
       <c r="H32" s="3">
-        <v>-17000</v>
+        <v>-114000</v>
       </c>
       <c r="I32" s="3">
-        <v>-198000</v>
+        <v>49000</v>
       </c>
       <c r="J32" s="3">
-        <v>-126000</v>
+        <v>-45000</v>
       </c>
       <c r="K32" s="3">
         <v>9000</v>
@@ -1425,7 +1425,7 @@
         <v>2173000</v>
       </c>
       <c r="J33" s="3">
-        <v>2207000</v>
+        <v>2213000</v>
       </c>
       <c r="K33" s="3">
         <v>1915000</v>
@@ -1485,7 +1485,7 @@
         <v>2173000</v>
       </c>
       <c r="J35" s="3">
-        <v>2207000</v>
+        <v>2213000</v>
       </c>
       <c r="K35" s="3">
         <v>1915000</v>
@@ -1572,7 +1572,7 @@
         <v>3278000</v>
       </c>
       <c r="H41" s="3">
-        <v>3544000</v>
+        <v>3508000</v>
       </c>
       <c r="I41" s="3">
         <v>3445000</v>
@@ -1590,25 +1590,25 @@
         <v>34</v>
       </c>
       <c r="D42" s="3">
-        <v>2087000</v>
+        <v>1929000</v>
       </c>
       <c r="E42" s="3">
-        <v>894000</v>
+        <v>730000</v>
       </c>
       <c r="F42" s="3">
-        <v>1308000</v>
+        <v>1180000</v>
       </c>
       <c r="G42" s="3">
-        <v>2400000</v>
+        <v>2116000</v>
       </c>
       <c r="H42" s="3">
-        <v>675000</v>
+        <v>566000</v>
       </c>
       <c r="I42" s="3">
-        <v>852000</v>
+        <v>712000</v>
       </c>
       <c r="J42" s="3">
-        <v>1263000</v>
+        <v>1083000</v>
       </c>
       <c r="K42" s="3">
         <v>2209000</v>
@@ -1638,7 +1638,7 @@
         <v>7468000</v>
       </c>
       <c r="J43" s="3">
-        <v>17418000</v>
+        <v>7002000</v>
       </c>
       <c r="K43" s="3">
         <v>9696000</v>
@@ -1668,7 +1668,7 @@
         <v>4284000</v>
       </c>
       <c r="J44" s="3">
-        <v>8796000</v>
+        <v>3737000</v>
       </c>
       <c r="K44" s="3">
         <v>4347000</v>
@@ -1680,25 +1680,25 @@
         <v>37</v>
       </c>
       <c r="D45" s="3">
-        <v>614000</v>
+        <v>519000</v>
       </c>
       <c r="E45" s="3">
-        <v>680000</v>
+        <v>596000</v>
       </c>
       <c r="F45" s="3">
-        <v>807000</v>
+        <v>699000</v>
       </c>
       <c r="G45" s="3">
-        <v>1274000</v>
+        <v>1034000</v>
       </c>
       <c r="H45" s="3">
-        <v>10596000</v>
+        <v>10514000</v>
       </c>
       <c r="I45" s="3">
-        <v>5816000</v>
+        <v>5780000</v>
       </c>
       <c r="J45" s="3">
-        <v>5607000</v>
+        <v>5628000</v>
       </c>
       <c r="K45" s="3">
         <v>2044000</v>
@@ -1740,25 +1740,25 @@
         <v>39</v>
       </c>
       <c r="D47" s="3">
-        <v>222000</v>
+        <v>187000</v>
       </c>
       <c r="E47" s="3">
-        <v>157000</v>
+        <v>130000</v>
       </c>
       <c r="F47" s="3">
-        <v>1691000</v>
+        <v>1690000</v>
       </c>
       <c r="G47" s="3">
-        <v>1808000</v>
+        <v>1862000</v>
       </c>
       <c r="H47" s="3">
-        <v>81000</v>
+        <v>105000</v>
       </c>
       <c r="I47" s="3">
-        <v>142000</v>
+        <v>122000</v>
       </c>
       <c r="J47" s="3">
-        <v>559000</v>
+        <v>113000</v>
       </c>
       <c r="K47" s="3">
         <v>394000</v>
@@ -1788,7 +1788,7 @@
         <v>4133000</v>
       </c>
       <c r="J48" s="3">
-        <v>9167000</v>
+        <v>3804000</v>
       </c>
       <c r="K48" s="3">
         <v>4743000</v>
@@ -1806,10 +1806,10 @@
         <v>11917000</v>
       </c>
       <c r="F49" s="3">
-        <v>12043000</v>
+        <v>12041000</v>
       </c>
       <c r="G49" s="3">
-        <v>12928000</v>
+        <v>12927000</v>
       </c>
       <c r="H49" s="3">
         <v>13077000</v>
@@ -1818,7 +1818,7 @@
         <v>13371000</v>
       </c>
       <c r="J49" s="3">
-        <v>14583000</v>
+        <v>11961000</v>
       </c>
       <c r="K49" s="3">
         <v>11497000</v>
@@ -1890,25 +1890,25 @@
         <v>44</v>
       </c>
       <c r="D52" s="3">
-        <v>2622000</v>
+        <v>1276000</v>
       </c>
       <c r="E52" s="3">
-        <v>2752000</v>
+        <v>1383000</v>
       </c>
       <c r="F52" s="3">
-        <v>2891000</v>
+        <v>1717000</v>
       </c>
       <c r="G52" s="3">
-        <v>1983000</v>
+        <v>1087000</v>
       </c>
       <c r="H52" s="3">
-        <v>1526000</v>
+        <v>592000</v>
       </c>
       <c r="I52" s="3">
-        <v>4930000</v>
+        <v>3913000</v>
       </c>
       <c r="J52" s="3">
-        <v>5171000</v>
+        <v>4203000</v>
       </c>
       <c r="K52" s="3">
         <v>1516000</v>
@@ -2038,25 +2038,25 @@
         <v>50</v>
       </c>
       <c r="D58" s="3">
-        <v>2607000</v>
+        <v>2875000</v>
       </c>
       <c r="E58" s="3">
-        <v>2535000</v>
+        <v>2763000</v>
       </c>
       <c r="F58" s="3">
-        <v>1384000</v>
+        <v>1616000</v>
       </c>
       <c r="G58" s="3">
-        <v>1293000</v>
+        <v>1565000</v>
       </c>
       <c r="H58" s="3">
-        <v>2287000</v>
+        <v>2592000</v>
       </c>
       <c r="I58" s="3">
         <v>2031000</v>
       </c>
       <c r="J58" s="3">
-        <v>726000</v>
+        <v>728000</v>
       </c>
       <c r="K58" s="3">
         <v>1003000</v>
@@ -2068,25 +2068,25 @@
         <v>51</v>
       </c>
       <c r="D59" s="3">
-        <v>10550000</v>
+        <v>6766000</v>
       </c>
       <c r="E59" s="3">
-        <v>9090000</v>
+        <v>5691000</v>
       </c>
       <c r="F59" s="3">
-        <v>9263000</v>
+        <v>5853000</v>
       </c>
       <c r="G59" s="3">
-        <v>9552000</v>
+        <v>6313000</v>
       </c>
       <c r="H59" s="3">
-        <v>13626000</v>
+        <v>10516000</v>
       </c>
       <c r="I59" s="3">
-        <v>11992000</v>
+        <v>9091000</v>
       </c>
       <c r="J59" s="3">
-        <v>14625000</v>
+        <v>9419000</v>
       </c>
       <c r="K59" s="3">
         <v>10501000</v>
@@ -2128,25 +2128,25 @@
         <v>53</v>
       </c>
       <c r="D61" s="3">
-        <v>5221000</v>
+        <v>6117000</v>
       </c>
       <c r="E61" s="3">
-        <v>5143000</v>
+        <v>6139000</v>
       </c>
       <c r="F61" s="3">
-        <v>4177000</v>
+        <v>4975000</v>
       </c>
       <c r="G61" s="3">
-        <v>4828000</v>
+        <v>5559000</v>
       </c>
       <c r="H61" s="3">
-        <v>6772000</v>
+        <v>7489000</v>
       </c>
       <c r="I61" s="3">
-        <v>6587000</v>
+        <v>6588000</v>
       </c>
       <c r="J61" s="3">
-        <v>6682000</v>
+        <v>6686000</v>
       </c>
       <c r="K61" s="3">
         <v>5800000</v>
@@ -2158,25 +2158,25 @@
         <v>54</v>
       </c>
       <c r="D62" s="3">
-        <v>3569000</v>
+        <v>1318000</v>
       </c>
       <c r="E62" s="3">
-        <v>4184000</v>
+        <v>1760000</v>
       </c>
       <c r="F62" s="3">
-        <v>4515000</v>
+        <v>1976000</v>
       </c>
       <c r="G62" s="3">
-        <v>4648000</v>
+        <v>2084000</v>
       </c>
       <c r="H62" s="3">
-        <v>5090000</v>
+        <v>1662000</v>
       </c>
       <c r="I62" s="3">
-        <v>4444000</v>
+        <v>2105000</v>
       </c>
       <c r="J62" s="3">
-        <v>6370000</v>
+        <v>2304000</v>
       </c>
       <c r="K62" s="3">
         <v>7524000</v>
@@ -2278,25 +2278,25 @@
         <v>57</v>
       </c>
       <c r="D66" s="3">
-        <v>27530000</v>
+        <v>26794000</v>
       </c>
       <c r="E66" s="3">
-        <v>26371000</v>
+        <v>25876000</v>
       </c>
       <c r="F66" s="3">
-        <v>24681000</v>
+        <v>24303000</v>
       </c>
       <c r="G66" s="3">
-        <v>25403000</v>
+        <v>25089000</v>
       </c>
       <c r="H66" s="3">
-        <v>32582000</v>
+        <v>32128000</v>
       </c>
       <c r="I66" s="3">
-        <v>30489000</v>
+        <v>29907000</v>
       </c>
       <c r="J66" s="3">
-        <v>28639000</v>
+        <v>28109000</v>
       </c>
       <c r="K66" s="3">
         <v>25807000</v>
@@ -2675,7 +2675,7 @@
         <v>2173000</v>
       </c>
       <c r="J81" s="3">
-        <v>2207000</v>
+        <v>2213000</v>
       </c>
       <c r="K81" s="3">
         <v>1915000</v>
@@ -2701,25 +2701,25 @@
         <v>71</v>
       </c>
       <c r="D83" s="3">
-        <v>780000</v>
+        <v>517000</v>
       </c>
       <c r="E83" s="3">
-        <v>814000</v>
+        <v>532000</v>
       </c>
       <c r="F83" s="3">
-        <v>893000</v>
+        <v>575000</v>
       </c>
       <c r="G83" s="3">
-        <v>915000</v>
+        <v>586000</v>
       </c>
       <c r="H83" s="3">
-        <v>961000</v>
+        <v>616000</v>
       </c>
       <c r="I83" s="3">
-        <v>916000</v>
+        <v>578000</v>
       </c>
       <c r="J83" s="3">
-        <v>836000</v>
+        <v>549000</v>
       </c>
       <c r="K83" s="3">
         <v>870000</v>
@@ -3059,25 +3059,25 @@
         <v>84</v>
       </c>
       <c r="D96" s="3">
-        <v>-1713000</v>
+        <v>1713000</v>
       </c>
       <c r="E96" s="3">
-        <v>-1698000</v>
+        <v>1698000</v>
       </c>
       <c r="F96" s="3">
-        <v>-1726000</v>
+        <v>1726000</v>
       </c>
       <c r="G96" s="3">
-        <v>-1736000</v>
+        <v>1736000</v>
       </c>
       <c r="H96" s="3">
-        <v>-1675000</v>
+        <v>1675000</v>
       </c>
       <c r="I96" s="3">
-        <v>-1717000</v>
+        <v>1717000</v>
       </c>
       <c r="J96" s="3">
-        <v>-1635000</v>
+        <v>1635000</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>

--- a/AAII_Financials/Yearly/ABBNY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ABBNY_YR_FIN.xlsx
@@ -653,147 +653,159 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M7" s="2"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>32850000</v>
+      </c>
+      <c r="E8" s="3">
         <v>32235000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>29446000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>28945000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>26134000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>27978000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>27662000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>25196000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>24929000</v>
       </c>
-      <c r="L8" s="3"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M8" s="3"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>20536000</v>
+      </c>
+      <c r="E9" s="3">
         <v>20956000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>19712000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>19407000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>18123000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>19018000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>19059000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>17278000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>17384000</v>
       </c>
-      <c r="L9" s="3"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M9" s="3"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>12314000</v>
+      </c>
+      <c r="E10" s="3">
         <v>11279000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>9734000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>9538000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>8011000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>8960000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>8603000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>7918000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>7545000</v>
       </c>
-      <c r="L10" s="3"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M10" s="3"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -806,38 +818,42 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>1458000</v>
+      </c>
+      <c r="E12" s="3">
         <v>1314000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1164000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1217000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1113000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>1197000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1142000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1018000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>956000</v>
       </c>
-      <c r="L12" s="3"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M12" s="3"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -865,69 +881,78 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-      <c r="L13" s="3"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>-31000</v>
+        <v>269000</v>
       </c>
       <c r="E14" s="3">
-        <v>176000</v>
+        <v>5000</v>
       </c>
       <c r="F14" s="3">
+        <v>180000</v>
+      </c>
+      <c r="G14" s="3">
         <v>-2164000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>718000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>458000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>67000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-185000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>196000</v>
       </c>
-      <c r="L14" s="3"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M14" s="3"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>754000</v>
+      </c>
+      <c r="E15" s="3">
         <v>736000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>762000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>827000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>854000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>887000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>857000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>786000</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
-      <c r="L15" s="3"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L15" s="3">
+        <v>0</v>
+      </c>
+      <c r="M15" s="3"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -937,68 +962,75 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>27371000</v>
+        <v>27443000</v>
       </c>
       <c r="E17" s="3">
-        <v>25757000</v>
+        <v>27335000</v>
       </c>
       <c r="F17" s="3">
+        <v>25753000</v>
+      </c>
+      <c r="G17" s="3">
         <v>25116000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>24320000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>25518000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>25292000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>23053000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>23000000</v>
       </c>
-      <c r="L17" s="3"/>
-    </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M17" s="3"/>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>4864000</v>
+        <v>5407000</v>
       </c>
       <c r="E18" s="3">
-        <v>3689000</v>
+        <v>4900000</v>
       </c>
       <c r="F18" s="3">
+        <v>3693000</v>
+      </c>
+      <c r="G18" s="3">
         <v>3829000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1814000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>2460000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>2370000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>2143000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1929000</v>
       </c>
-      <c r="L18" s="3"/>
-    </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M18" s="3"/>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1011,158 +1043,174 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>271000</v>
+        <v>-270000</v>
       </c>
       <c r="E20" s="3">
-        <v>194000</v>
+        <v>247000</v>
       </c>
       <c r="F20" s="3">
+        <v>189000</v>
+      </c>
+      <c r="G20" s="3">
         <v>255000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-142000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>114000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-49000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>45000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-9000</v>
       </c>
-      <c r="L20" s="3"/>
-    </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M20" s="3"/>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>5329000</v>
+        <v>6431000</v>
       </c>
       <c r="E21" s="3">
-        <v>4257000</v>
+        <v>5389000</v>
       </c>
       <c r="F21" s="3">
+        <v>4266000</v>
+      </c>
+      <c r="G21" s="3">
         <v>4401000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>2810000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>3233000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>3276000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2884000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2790000</v>
       </c>
-      <c r="L21" s="3"/>
-    </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M21" s="3"/>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
-        <v>11000</v>
+        <v>381000</v>
       </c>
       <c r="E22" s="3">
-        <v>3000</v>
+        <v>35000</v>
       </c>
       <c r="F22" s="3">
         <v>2000</v>
       </c>
       <c r="G22" s="3">
+        <v>2000</v>
+      </c>
+      <c r="H22" s="3">
         <v>448000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>93000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>305000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>254000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>159000</v>
       </c>
-      <c r="L22" s="3"/>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M22" s="3"/>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>5233000</v>
+      </c>
+      <c r="E23" s="3">
         <v>4778000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>3394000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>5787000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>841000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1862000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2119000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2102000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1761000</v>
       </c>
-      <c r="L23" s="3"/>
-    </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M23" s="3"/>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>1278000</v>
+      </c>
+      <c r="E24" s="3">
         <v>930000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>757000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1057000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>496000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>772000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>544000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>583000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>526000</v>
       </c>
-      <c r="L24" s="3"/>
-    </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M24" s="3"/>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1190,69 +1238,78 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-      <c r="L25" s="3"/>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3"/>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>3955000</v>
+      </c>
+      <c r="E26" s="3">
         <v>3848000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>2637000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>4730000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>345000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1090000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1575000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1519000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1235000</v>
       </c>
-      <c r="L26" s="3"/>
-    </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M26" s="3"/>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>3935000</v>
+      </c>
+      <c r="E27" s="3">
         <v>3745000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>2475000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>4546000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>5146000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1439000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>2173000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>2213000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1100000</v>
       </c>
-      <c r="L27" s="3"/>
-    </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M27" s="3"/>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1280,39 +1337,45 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-      <c r="L28" s="3"/>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3"/>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D29" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E29" s="3">
         <v>-24000</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>-43000</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>-80000</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>4860000</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>438000</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>723000</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>846000</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>815000</v>
       </c>
-      <c r="L29" s="3"/>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M29" s="3"/>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -1340,9 +1403,12 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-      <c r="L30" s="3"/>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3"/>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -1370,69 +1436,78 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-      <c r="L31" s="3"/>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3"/>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
-        <v>-271000</v>
+        <v>270000</v>
       </c>
       <c r="E32" s="3">
-        <v>-194000</v>
+        <v>-247000</v>
       </c>
       <c r="F32" s="3">
+        <v>-189000</v>
+      </c>
+      <c r="G32" s="3">
         <v>-255000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>142000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-114000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>49000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-45000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>9000</v>
       </c>
-      <c r="L32" s="3"/>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M32" s="3"/>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>3935000</v>
+      </c>
+      <c r="E33" s="3">
         <v>3745000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>2475000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>4546000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>5146000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1439000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>2173000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>2213000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1915000</v>
       </c>
-      <c r="L33" s="3"/>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M33" s="3"/>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -1460,74 +1535,83 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-      <c r="L34" s="3"/>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3"/>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>3935000</v>
+      </c>
+      <c r="E35" s="3">
         <v>3745000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>2475000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>4546000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>5146000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1439000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>2173000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>2213000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1915000</v>
       </c>
-      <c r="L35" s="3"/>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M35" s="3"/>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2"/>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M38" s="2"/>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -1540,8 +1624,9 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -1554,278 +1639,306 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>4311000</v>
+      </c>
+      <c r="E41" s="3">
         <v>3891000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>4156000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4159000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3278000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3508000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3445000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>4526000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3644000</v>
       </c>
-      <c r="L41" s="3"/>
-    </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M41" s="3"/>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
+        <v>1334000</v>
+      </c>
+      <c r="E42" s="3">
         <v>1929000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>730000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1180000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>2116000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>566000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>712000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1083000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>2209000</v>
       </c>
-      <c r="L42" s="3"/>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M42" s="3"/>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>8503000</v>
+      </c>
+      <c r="E43" s="3">
         <v>8536000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>7812000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>7541000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>7805000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>7459000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>7468000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>7002000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>9696000</v>
       </c>
-      <c r="L43" s="3"/>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M43" s="3"/>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>5859000</v>
+      </c>
+      <c r="E44" s="3">
         <v>6149000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>6028000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>4880000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>4469000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>4184000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>4284000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>3737000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>4347000</v>
       </c>
-      <c r="L44" s="3"/>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M44" s="3"/>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
+        <v>541000</v>
+      </c>
+      <c r="E45" s="3">
         <v>519000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>596000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>699000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1034000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>10514000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>5780000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>5628000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2044000</v>
       </c>
-      <c r="L45" s="3"/>
-    </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M45" s="3"/>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>20850000</v>
+      </c>
+      <c r="E46" s="3">
         <v>21277000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>19570000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>18695000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>19226000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>26458000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>21865000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>22135000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>21052000</v>
       </c>
-      <c r="L46" s="3"/>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M46" s="3"/>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
+        <v>375000</v>
+      </c>
+      <c r="E47" s="3">
         <v>187000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>130000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1690000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1862000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>105000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>122000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>113000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>394000</v>
       </c>
-      <c r="L47" s="3"/>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M47" s="3"/>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>5017000</v>
+      </c>
+      <c r="E48" s="3">
         <v>5035000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4752000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4940000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>5143000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4966000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4133000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3804000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4743000</v>
       </c>
-      <c r="L48" s="3"/>
-    </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M48" s="3"/>
+    </row>
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>11603000</v>
+      </c>
+      <c r="E49" s="3">
         <v>11784000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>11917000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>12041000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>12927000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>13077000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>13371000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>11961000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>11497000</v>
       </c>
-      <c r="L49" s="3"/>
-    </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M49" s="3"/>
+    </row>
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -1853,9 +1966,12 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-      <c r="L50" s="3"/>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3"/>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -1883,39 +1999,45 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-      <c r="L51" s="3"/>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3"/>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
+        <v>1171000</v>
+      </c>
+      <c r="E52" s="3">
         <v>1276000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1383000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1717000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1087000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>592000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>3913000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4203000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1516000</v>
       </c>
-      <c r="L52" s="3"/>
-    </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M52" s="3"/>
+    </row>
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -1943,39 +2065,45 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-      <c r="L53" s="3"/>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+      <c r="M53" s="3"/>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>40357000</v>
+      </c>
+      <c r="E54" s="3">
         <v>40940000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>39148000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>40260000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>41088000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>46108000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>44441000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>43458000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>39202000</v>
       </c>
-      <c r="L54" s="3"/>
-    </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M54" s="3"/>
+    </row>
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -1988,8 +2116,9 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -2002,188 +2131,207 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>5036000</v>
+      </c>
+      <c r="E57" s="3">
         <v>4847000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4904000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4921000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4571000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4353000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>4424000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3736000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>4446000</v>
       </c>
-      <c r="L57" s="3"/>
-    </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M57" s="3"/>
+    </row>
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
+        <v>528000</v>
+      </c>
+      <c r="E58" s="3">
         <v>2875000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2763000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1616000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1565000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2592000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2031000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>728000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1003000</v>
       </c>
-      <c r="L58" s="3"/>
-    </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M58" s="3"/>
+    </row>
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
+        <v>6321000</v>
+      </c>
+      <c r="E59" s="3">
         <v>6766000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>5691000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>5853000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>6313000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>10516000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>9091000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>9419000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>10501000</v>
       </c>
-      <c r="L59" s="3"/>
-    </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M59" s="3"/>
+    </row>
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>15216000</v>
+      </c>
+      <c r="E60" s="3">
         <v>18004000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>16529000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>15568000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>15416000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>20266000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>18447000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>16469000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>15149000</v>
       </c>
-      <c r="L60" s="3"/>
-    </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M60" s="3"/>
+    </row>
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
+        <v>7539000</v>
+      </c>
+      <c r="E61" s="3">
         <v>6117000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>6139000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4975000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>5559000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>7489000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>6588000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>6686000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>5800000</v>
       </c>
-      <c r="L61" s="3"/>
-    </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M61" s="3"/>
+    </row>
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
+        <v>1298000</v>
+      </c>
+      <c r="E62" s="3">
         <v>1318000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1760000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1976000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2084000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1662000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2105000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2304000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>7524000</v>
       </c>
-      <c r="L62" s="3"/>
-    </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M62" s="3"/>
+    </row>
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -2211,9 +2359,12 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-      <c r="L63" s="3"/>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+      <c r="M63" s="3"/>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -2241,9 +2392,12 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-      <c r="L64" s="3"/>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3"/>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -2271,39 +2425,45 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-      <c r="L65" s="3"/>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+      <c r="M65" s="3"/>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>25297000</v>
+      </c>
+      <c r="E66" s="3">
         <v>26794000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>25876000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>24303000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>25089000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>32128000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>29907000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>28109000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>25807000</v>
       </c>
-      <c r="L66" s="3"/>
-    </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M66" s="3"/>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -2316,8 +2476,9 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -2345,9 +2506,12 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-      <c r="L68" s="3"/>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+      <c r="M68" s="3"/>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -2375,9 +2539,12 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-      <c r="L69" s="3"/>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3"/>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -2405,9 +2572,12 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-      <c r="L70" s="3"/>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3"/>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -2435,39 +2605,45 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-      <c r="L71" s="3"/>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+      <c r="M71" s="3"/>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>20717000</v>
+      </c>
+      <c r="E72" s="3">
         <v>19724000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>20082000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>22477000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>22946000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>19640000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>19839000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>19594000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>19925000</v>
       </c>
-      <c r="L72" s="3"/>
-    </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M72" s="3"/>
+    </row>
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -2495,9 +2671,12 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-      <c r="L73" s="3"/>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+      <c r="M73" s="3"/>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -2525,9 +2704,12 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-      <c r="L74" s="3"/>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+      <c r="M74" s="3"/>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -2555,39 +2737,45 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-      <c r="L75" s="3"/>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+      <c r="M75" s="3"/>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>14488000</v>
+      </c>
+      <c r="E76" s="3">
         <v>13410000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>12777000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>15579000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>15685000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>13526000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>13952000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>14819000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>13395000</v>
       </c>
-      <c r="L76" s="3"/>
-    </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M76" s="3"/>
+    </row>
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -2615,74 +2803,83 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-      <c r="L77" s="3"/>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+      <c r="M77" s="3"/>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2"/>
-    </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M80" s="2"/>
+    </row>
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>3935000</v>
+      </c>
+      <c r="E81" s="3">
         <v>3745000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>2475000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>4546000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>5146000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1439000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>2173000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>2213000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1915000</v>
       </c>
-      <c r="L81" s="3"/>
-    </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M81" s="3"/>
+    </row>
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -2695,38 +2892,42 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
+        <v>550000</v>
+      </c>
+      <c r="E83" s="3">
         <v>517000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>532000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>575000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>586000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>616000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>578000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>549000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>870000</v>
       </c>
-      <c r="L83" s="3"/>
-    </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M83" s="3"/>
+    </row>
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -2754,9 +2955,12 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-      <c r="L84" s="3"/>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+      <c r="M84" s="3"/>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -2784,9 +2988,12 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-      <c r="L85" s="3"/>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+      <c r="M85" s="3"/>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -2814,9 +3021,12 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-      <c r="L86" s="3"/>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+      <c r="M86" s="3"/>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -2844,9 +3054,12 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-      <c r="L87" s="3"/>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+      <c r="M87" s="3"/>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -2874,39 +3087,45 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-      <c r="L88" s="3"/>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3"/>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>4675000</v>
+      </c>
+      <c r="E89" s="3">
         <v>4290000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1287000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>3330000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1693000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2325000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2924000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>3799000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3843000</v>
       </c>
-      <c r="L89" s="3"/>
-    </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M89" s="3"/>
+    </row>
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -2919,38 +3138,42 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-845000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-770000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-762000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-820000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-694000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-762000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-772000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-752000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-632000</v>
       </c>
-      <c r="L91" s="3"/>
-    </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M91" s="3"/>
+    </row>
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -2978,9 +3201,12 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-      <c r="L92" s="3"/>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+      <c r="M92" s="3"/>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -3008,39 +3234,45 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-      <c r="L93" s="3"/>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+      <c r="M93" s="3"/>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>-725000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1615000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>981000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>2307000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>6760000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-815000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3085000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1450000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1305000</v>
       </c>
-      <c r="L94" s="3"/>
-    </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M94" s="3"/>
+    </row>
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -3053,38 +3285,42 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D96" s="3">
+        <v>1769000</v>
+      </c>
+      <c r="E96" s="3">
         <v>1713000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>1698000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>1726000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>1736000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>1675000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>1717000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>1635000</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3"/>
-    </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3"/>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -3112,9 +3348,12 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-      <c r="L97" s="3"/>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+      <c r="M97" s="3"/>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -3142,9 +3381,12 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-      <c r="L98" s="3"/>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+      <c r="M98" s="3"/>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -3172,97 +3414,109 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-      <c r="L99" s="3"/>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+      <c r="M99" s="3"/>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>-3326000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2897000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-2394000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-4968000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-8175000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1383000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-789000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1735000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-3355000</v>
       </c>
-      <c r="L100" s="3"/>
-    </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M100" s="3"/>
+    </row>
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
+        <v>-207000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-43000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-189000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-81000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>79000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-28000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-131000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>268000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-104000</v>
       </c>
-      <c r="L101" s="3"/>
-    </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M101" s="3"/>
+    </row>
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>417000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-265000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-315000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>588000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>357000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>99000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1081000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>882000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-921000</v>
       </c>
-      <c r="L102" s="3"/>
+      <c r="M102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/ABBNY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ABBNY_YR_FIN.xlsx
@@ -653,159 +653,171 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N7" s="2"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>32850000</v>
+        <v>33220000</v>
       </c>
       <c r="E8" s="3">
+        <v>30583000</v>
+      </c>
+      <c r="F8" s="3">
         <v>32235000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>29446000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>28945000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>26134000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>27978000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>27662000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>25196000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>24929000</v>
       </c>
-      <c r="M8" s="3"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N8" s="3"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>20536000</v>
+        <v>19580000</v>
       </c>
       <c r="E9" s="3">
+        <v>18582000</v>
+      </c>
+      <c r="F9" s="3">
         <v>20956000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>19712000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>19407000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>18123000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>19018000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>19059000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>17278000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>17384000</v>
       </c>
-      <c r="M9" s="3"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N9" s="3"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>12314000</v>
+        <v>13640000</v>
       </c>
       <c r="E10" s="3">
+        <v>12001000</v>
+      </c>
+      <c r="F10" s="3">
         <v>11279000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>9734000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>9538000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>8011000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>8960000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>8603000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>7918000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>7545000</v>
       </c>
-      <c r="M10" s="3"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N10" s="3"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -819,41 +831,45 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>1458000</v>
+        <v>1318000</v>
       </c>
       <c r="E12" s="3">
+        <v>1268000</v>
+      </c>
+      <c r="F12" s="3">
         <v>1314000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1164000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1217000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>1113000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1197000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1142000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>1018000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>956000</v>
       </c>
-      <c r="M12" s="3"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N12" s="3"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -884,75 +900,84 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-      <c r="M13" s="3"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+      <c r="N13" s="3"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>269000</v>
+        <v>-192000</v>
       </c>
       <c r="E14" s="3">
+        <v>167000</v>
+      </c>
+      <c r="F14" s="3">
         <v>5000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>180000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-2164000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>718000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>458000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>67000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-185000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>196000</v>
       </c>
-      <c r="M14" s="3"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N14" s="3"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>754000</v>
+        <v>766000</v>
       </c>
       <c r="E15" s="3">
+        <v>715000</v>
+      </c>
+      <c r="F15" s="3">
         <v>736000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>762000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>827000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>854000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>887000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>857000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>786000</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
-      <c r="M15" s="3"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -963,74 +988,81 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>27443000</v>
+        <v>27310000</v>
       </c>
       <c r="E17" s="3">
+        <v>25625000</v>
+      </c>
+      <c r="F17" s="3">
         <v>27335000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>25753000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>25116000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>24320000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>25518000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>25292000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>23053000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>23000000</v>
       </c>
-      <c r="M17" s="3"/>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N17" s="3"/>
+    </row>
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>5407000</v>
+        <v>5910000</v>
       </c>
       <c r="E18" s="3">
+        <v>4958000</v>
+      </c>
+      <c r="F18" s="3">
         <v>4900000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>3693000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>3829000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1814000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>2460000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>2370000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2143000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1929000</v>
       </c>
-      <c r="M18" s="3"/>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N18" s="3"/>
+    </row>
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1044,173 +1076,189 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>-270000</v>
+        <v>89000</v>
       </c>
       <c r="E20" s="3">
+        <v>-282000</v>
+      </c>
+      <c r="F20" s="3">
         <v>247000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>189000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>255000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-142000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>114000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-49000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>45000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-9000</v>
       </c>
-      <c r="M20" s="3"/>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N20" s="3"/>
+    </row>
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>6431000</v>
+        <v>6587000</v>
       </c>
       <c r="E21" s="3">
+        <v>5955000</v>
+      </c>
+      <c r="F21" s="3">
         <v>5389000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>4266000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>4401000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>2810000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>3233000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>3276000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2884000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2790000</v>
       </c>
-      <c r="M21" s="3"/>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N21" s="3"/>
+    </row>
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
-        <v>381000</v>
+        <v>3000</v>
       </c>
       <c r="E22" s="3">
+        <v>356000</v>
+      </c>
+      <c r="F22" s="3">
         <v>35000</v>
-      </c>
-      <c r="F22" s="3">
-        <v>2000</v>
       </c>
       <c r="G22" s="3">
         <v>2000</v>
       </c>
       <c r="H22" s="3">
+        <v>2000</v>
+      </c>
+      <c r="I22" s="3">
         <v>448000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>93000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>305000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>254000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>159000</v>
       </c>
-      <c r="M22" s="3"/>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N22" s="3"/>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
-        <v>5233000</v>
+        <v>6219000</v>
       </c>
       <c r="E23" s="3">
+        <v>4923000</v>
+      </c>
+      <c r="F23" s="3">
         <v>4778000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>3394000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>5787000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>841000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1862000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2119000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2102000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1761000</v>
       </c>
-      <c r="M23" s="3"/>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N23" s="3"/>
+    </row>
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
-        <v>1278000</v>
+        <v>1570000</v>
       </c>
       <c r="E24" s="3">
+        <v>1197000</v>
+      </c>
+      <c r="F24" s="3">
         <v>930000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>757000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1057000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>496000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>772000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>544000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>583000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>526000</v>
       </c>
-      <c r="M24" s="3"/>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N24" s="3"/>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1241,75 +1289,84 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-      <c r="M25" s="3"/>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+      <c r="N25" s="3"/>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
-        <v>3955000</v>
+        <v>4649000</v>
       </c>
       <c r="E26" s="3">
+        <v>3726000</v>
+      </c>
+      <c r="F26" s="3">
         <v>3848000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>2637000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>4730000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>345000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1090000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1575000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1519000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1235000</v>
       </c>
-      <c r="M26" s="3"/>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N26" s="3"/>
+    </row>
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>4734000</v>
+      </c>
+      <c r="E27" s="3">
         <v>3935000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>3745000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>2475000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>4546000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>5146000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1439000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>2173000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2213000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1100000</v>
       </c>
-      <c r="M27" s="3"/>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N27" s="3"/>
+    </row>
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1340,42 +1397,48 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-      <c r="M28" s="3"/>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+      <c r="N28" s="3"/>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D29" s="3">
-        <v>-3000</v>
+        <v>174000</v>
       </c>
       <c r="E29" s="3">
+        <v>226000</v>
+      </c>
+      <c r="F29" s="3">
         <v>-24000</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>-43000</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>-80000</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>4860000</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>438000</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>723000</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>846000</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>815000</v>
       </c>
-      <c r="M29" s="3"/>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N29" s="3"/>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -1406,9 +1469,12 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-      <c r="M30" s="3"/>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+      <c r="N30" s="3"/>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -1439,75 +1505,84 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-      <c r="M31" s="3"/>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+      <c r="N31" s="3"/>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
-        <v>270000</v>
+        <v>-89000</v>
       </c>
       <c r="E32" s="3">
+        <v>282000</v>
+      </c>
+      <c r="F32" s="3">
         <v>-247000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-189000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-255000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>142000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-114000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>49000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-45000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>9000</v>
       </c>
-      <c r="M32" s="3"/>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N32" s="3"/>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>4734000</v>
+      </c>
+      <c r="E33" s="3">
         <v>3935000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>3745000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>2475000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>4546000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>5146000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1439000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>2173000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2213000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1915000</v>
       </c>
-      <c r="M33" s="3"/>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N33" s="3"/>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -1538,80 +1613,89 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-      <c r="M34" s="3"/>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+      <c r="N34" s="3"/>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>4734000</v>
+      </c>
+      <c r="E35" s="3">
         <v>3935000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>3745000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>2475000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>4546000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>5146000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1439000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>2173000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2213000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1915000</v>
       </c>
-      <c r="M35" s="3"/>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N35" s="3"/>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2"/>
-    </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N38" s="2"/>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -1625,8 +1709,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -1640,305 +1725,333 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
-        <v>4311000</v>
+        <v>4640000</v>
       </c>
       <c r="E41" s="3">
+        <v>4326000</v>
+      </c>
+      <c r="F41" s="3">
         <v>3891000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4156000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>4159000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3278000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3508000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3445000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>4526000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3644000</v>
       </c>
-      <c r="M41" s="3"/>
-    </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N41" s="3"/>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
+        <v>1981000</v>
+      </c>
+      <c r="E42" s="3">
         <v>1334000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>1929000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>730000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1180000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>2116000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>566000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>712000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1083000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>2209000</v>
       </c>
-      <c r="M42" s="3"/>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N42" s="3"/>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
-        <v>8503000</v>
+        <v>8625000</v>
       </c>
       <c r="E43" s="3">
+        <v>7732000</v>
+      </c>
+      <c r="F43" s="3">
         <v>8536000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>7812000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>7541000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>7805000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>7459000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>7468000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>7002000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>9696000</v>
       </c>
-      <c r="M43" s="3"/>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N43" s="3"/>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
-        <v>5859000</v>
+        <v>5862000</v>
       </c>
       <c r="E44" s="3">
+        <v>5420000</v>
+      </c>
+      <c r="F44" s="3">
         <v>6149000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>6028000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>4880000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>4469000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>4184000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>4284000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>3737000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>4347000</v>
       </c>
-      <c r="M44" s="3"/>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N44" s="3"/>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
-        <v>541000</v>
+        <v>4189000</v>
       </c>
       <c r="E45" s="3">
+        <v>1665000</v>
+      </c>
+      <c r="F45" s="3">
         <v>519000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>596000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>699000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1034000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>10514000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>5780000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>5628000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2044000</v>
       </c>
-      <c r="M45" s="3"/>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N45" s="3"/>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
-        <v>20850000</v>
+        <v>25578000</v>
       </c>
       <c r="E46" s="3">
+        <v>20759000</v>
+      </c>
+      <c r="F46" s="3">
         <v>21277000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>19570000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>18695000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>19226000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>26458000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>21865000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>22135000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>21052000</v>
       </c>
-      <c r="M46" s="3"/>
-    </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N46" s="3"/>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
-        <v>375000</v>
+        <v>351000</v>
       </c>
       <c r="E47" s="3">
+        <v>358000</v>
+      </c>
+      <c r="F47" s="3">
         <v>187000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>130000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1690000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1862000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>105000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>122000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>113000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>394000</v>
       </c>
-      <c r="M47" s="3"/>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N47" s="3"/>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
-        <v>5017000</v>
+        <v>5457000</v>
       </c>
       <c r="E48" s="3">
+        <v>4738000</v>
+      </c>
+      <c r="F48" s="3">
         <v>5035000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4752000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4940000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>5143000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4966000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4133000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3804000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4743000</v>
       </c>
-      <c r="M48" s="3"/>
-    </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N48" s="3"/>
+    </row>
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
-        <v>11603000</v>
+        <v>10753000</v>
       </c>
       <c r="E49" s="3">
+        <v>9800000</v>
+      </c>
+      <c r="F49" s="3">
         <v>11784000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>11917000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>12041000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>12927000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>13077000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>13371000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>11961000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>11497000</v>
       </c>
-      <c r="M49" s="3"/>
-    </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N49" s="3"/>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -1969,9 +2082,12 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-      <c r="M50" s="3"/>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+      <c r="N50" s="3"/>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -2002,42 +2118,48 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-      <c r="M51" s="3"/>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+      <c r="N51" s="3"/>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
-        <v>1171000</v>
+        <v>1498000</v>
       </c>
       <c r="E52" s="3">
+        <v>3334000</v>
+      </c>
+      <c r="F52" s="3">
         <v>1276000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1383000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1717000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1087000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>592000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>3913000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4203000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1516000</v>
       </c>
-      <c r="M52" s="3"/>
-    </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N52" s="3"/>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -2068,42 +2190,48 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-      <c r="M53" s="3"/>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+      <c r="N53" s="3"/>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
-        <v>40357000</v>
+        <v>44885000</v>
       </c>
       <c r="E54" s="3">
+        <v>40288000</v>
+      </c>
+      <c r="F54" s="3">
         <v>40940000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>39148000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>40260000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>41088000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>46108000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>44441000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>43458000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>39202000</v>
       </c>
-      <c r="M54" s="3"/>
-    </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N54" s="3"/>
+    </row>
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -2117,8 +2245,9 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -2132,206 +2261,225 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
-        <v>5036000</v>
+        <v>5210000</v>
       </c>
       <c r="E57" s="3">
+        <v>4681000</v>
+      </c>
+      <c r="F57" s="3">
         <v>4847000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4904000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4921000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4571000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>4353000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>4424000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3736000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>4446000</v>
       </c>
-      <c r="M57" s="3"/>
-    </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N57" s="3"/>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
-        <v>528000</v>
+        <v>728000</v>
       </c>
       <c r="E58" s="3">
+        <v>517000</v>
+      </c>
+      <c r="F58" s="3">
         <v>2875000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2763000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1616000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1565000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2592000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2031000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>728000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1003000</v>
       </c>
-      <c r="M58" s="3"/>
-    </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N58" s="3"/>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
-        <v>6321000</v>
+        <v>6957000</v>
       </c>
       <c r="E59" s="3">
+        <v>6264000</v>
+      </c>
+      <c r="F59" s="3">
         <v>6766000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>5691000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>5853000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>6313000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>10516000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>9091000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>9419000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>10501000</v>
       </c>
-      <c r="M59" s="3"/>
-    </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N59" s="3"/>
+    </row>
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
-        <v>15216000</v>
+        <v>16421000</v>
       </c>
       <c r="E60" s="3">
+        <v>14654000</v>
+      </c>
+      <c r="F60" s="3">
         <v>18004000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>16529000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>15568000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>15416000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>20266000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>18447000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>16469000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>15149000</v>
       </c>
-      <c r="M60" s="3"/>
-    </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N60" s="3"/>
+    </row>
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
-        <v>7539000</v>
+        <v>8508000</v>
       </c>
       <c r="E61" s="3">
+        <v>7447000</v>
+      </c>
+      <c r="F61" s="3">
         <v>6117000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>6139000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>4975000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>5559000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>7489000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>6588000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>6686000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>5800000</v>
       </c>
-      <c r="M61" s="3"/>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N61" s="3"/>
+    </row>
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
-        <v>1298000</v>
+        <v>1968000</v>
       </c>
       <c r="E62" s="3">
+        <v>2004000</v>
+      </c>
+      <c r="F62" s="3">
         <v>1318000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1760000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1976000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2084000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1662000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2105000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2304000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>7524000</v>
       </c>
-      <c r="M62" s="3"/>
-    </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N62" s="3"/>
+    </row>
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -2362,9 +2510,12 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-      <c r="M63" s="3"/>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+      <c r="N63" s="3"/>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -2395,9 +2546,12 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-      <c r="M64" s="3"/>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+      <c r="N64" s="3"/>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -2428,42 +2582,48 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-      <c r="M65" s="3"/>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+      <c r="N65" s="3"/>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>28239000</v>
+      </c>
+      <c r="E66" s="3">
         <v>25297000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>26794000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>25876000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>24303000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>25089000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>32128000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>29907000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>28109000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>25807000</v>
       </c>
-      <c r="M66" s="3"/>
-    </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N66" s="3"/>
+    </row>
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -2477,8 +2637,9 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -2509,9 +2670,12 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-      <c r="M68" s="3"/>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+      <c r="N68" s="3"/>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -2542,9 +2706,12 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-      <c r="M69" s="3"/>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+      <c r="N69" s="3"/>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -2575,9 +2742,12 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-      <c r="M70" s="3"/>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3"/>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -2608,42 +2778,48 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-      <c r="M71" s="3"/>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+      <c r="N71" s="3"/>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
-        <v>20717000</v>
+        <v>22606000</v>
       </c>
       <c r="E72" s="3">
+        <v>20648000</v>
+      </c>
+      <c r="F72" s="3">
         <v>19724000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>20082000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>22477000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>22946000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>19640000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>19839000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>19594000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>19925000</v>
       </c>
-      <c r="M72" s="3"/>
-    </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N72" s="3"/>
+    </row>
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -2674,9 +2850,12 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-      <c r="M73" s="3"/>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+      <c r="N73" s="3"/>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -2707,9 +2886,12 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-      <c r="M74" s="3"/>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+      <c r="N74" s="3"/>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -2740,42 +2922,48 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-      <c r="M75" s="3"/>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+      <c r="N75" s="3"/>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
-        <v>14488000</v>
+        <v>16087000</v>
       </c>
       <c r="E76" s="3">
+        <v>14419000</v>
+      </c>
+      <c r="F76" s="3">
         <v>13410000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>12777000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>15579000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>15685000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>13526000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>13952000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>14819000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>13395000</v>
       </c>
-      <c r="M76" s="3"/>
-    </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N76" s="3"/>
+    </row>
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -2806,80 +2994,89 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-      <c r="M77" s="3"/>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+      <c r="N77" s="3"/>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2"/>
-    </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N80" s="2"/>
+    </row>
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>4734000</v>
+      </c>
+      <c r="E81" s="3">
         <v>3935000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>3745000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>2475000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>4546000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>5146000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1439000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>2173000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2213000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1915000</v>
       </c>
-      <c r="M81" s="3"/>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N81" s="3"/>
+    </row>
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -2893,41 +3090,45 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
-        <v>550000</v>
+        <v>581000</v>
       </c>
       <c r="E83" s="3">
+        <v>520000</v>
+      </c>
+      <c r="F83" s="3">
         <v>517000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>532000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>575000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>586000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>616000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>578000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>549000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>870000</v>
       </c>
-      <c r="M83" s="3"/>
-    </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N83" s="3"/>
+    </row>
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -2958,9 +3159,12 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-      <c r="M84" s="3"/>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+      <c r="N84" s="3"/>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -2991,9 +3195,12 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-      <c r="M85" s="3"/>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+      <c r="N85" s="3"/>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -3024,9 +3231,12 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-      <c r="M86" s="3"/>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+      <c r="N86" s="3"/>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -3057,9 +3267,12 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-      <c r="M87" s="3"/>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+      <c r="N87" s="3"/>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -3090,42 +3303,48 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-      <c r="M88" s="3"/>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+      <c r="N88" s="3"/>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>5469000</v>
+      </c>
+      <c r="E89" s="3">
         <v>4675000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>4290000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1287000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>3330000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1693000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2325000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2924000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3799000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3843000</v>
       </c>
-      <c r="M89" s="3"/>
-    </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N89" s="3"/>
+    </row>
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -3139,41 +3358,45 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
-        <v>-845000</v>
+        <v>-1001000</v>
       </c>
       <c r="E91" s="3">
+        <v>-799000</v>
+      </c>
+      <c r="F91" s="3">
         <v>-770000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-762000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-820000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-694000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-762000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-772000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-752000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-632000</v>
       </c>
-      <c r="M91" s="3"/>
-    </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N91" s="3"/>
+    </row>
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -3204,9 +3427,12 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-      <c r="M92" s="3"/>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+      <c r="N92" s="3"/>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -3237,42 +3463,48 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-      <c r="M93" s="3"/>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+      <c r="N93" s="3"/>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>-2389000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-725000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1615000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>981000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>2307000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>6760000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-815000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3085000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1450000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1305000</v>
       </c>
-      <c r="M94" s="3"/>
-    </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N94" s="3"/>
+    </row>
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -3286,41 +3518,45 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D96" s="3">
+        <v>1907000</v>
+      </c>
+      <c r="E96" s="3">
         <v>1769000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>1713000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>1698000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>1726000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>1736000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>1675000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>1717000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>1635000</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
-      <c r="M96" s="3"/>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3"/>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -3351,9 +3587,12 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-      <c r="M97" s="3"/>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+      <c r="N97" s="3"/>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -3384,9 +3623,12 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-      <c r="M98" s="3"/>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+      <c r="N98" s="3"/>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -3417,106 +3659,118 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-      <c r="M99" s="3"/>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+      <c r="N99" s="3"/>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>-2877000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-3326000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-2897000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2394000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-4968000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-8175000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1383000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-789000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1735000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-3355000</v>
       </c>
-      <c r="M100" s="3"/>
-    </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N100" s="3"/>
+    </row>
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
+        <v>111000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-207000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-43000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-189000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-81000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>79000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-28000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-131000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>268000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-104000</v>
       </c>
-      <c r="M101" s="3"/>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N101" s="3"/>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>314000</v>
+      </c>
+      <c r="E102" s="3">
         <v>417000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-265000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-315000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>588000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>357000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>99000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1081000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>882000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-921000</v>
       </c>
-      <c r="M102" s="3"/>
+      <c r="N102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
